--- a/presentaciones.xlsx
+++ b/presentaciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juanc\OneDrive\Documentos\LAB-MAA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E7DFA3FE-97F1-499A-B02A-0216440C9EA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39111D3F-919D-4C0A-BA56-01D1AAFE5813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$1</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="107">
   <si>
     <t>Estudiante</t>
   </si>
@@ -905,7 +904,9 @@
       <c r="C7" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="D7" s="7"/>
+      <c r="D7" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="E7" s="2" t="s">
         <v>80</v>
       </c>
@@ -1154,6 +1155,9 @@
       <c r="C18" t="s">
         <v>102</v>
       </c>
+      <c r="D18" s="9" t="s">
+        <v>14</v>
+      </c>
       <c r="E18" t="s">
         <v>95</v>
       </c>
@@ -1243,6 +1247,9 @@
       <c r="C22" t="s">
         <v>100</v>
       </c>
+      <c r="D22" t="s">
+        <v>14</v>
+      </c>
       <c r="E22" s="2" t="s">
         <v>35</v>
       </c>
@@ -1263,6 +1270,9 @@
       <c r="C23" t="s">
         <v>100</v>
       </c>
+      <c r="D23" s="9" t="s">
+        <v>14</v>
+      </c>
       <c r="E23" s="2" t="s">
         <v>32</v>
       </c>
@@ -1396,7 +1406,9 @@
       <c r="C29" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="D29" s="9"/>
+      <c r="D29" s="9" t="s">
+        <v>14</v>
+      </c>
       <c r="E29" t="s">
         <v>20</v>
       </c>

--- a/presentaciones.xlsx
+++ b/presentaciones.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juanc\OneDrive\Documentos\LAB-MAA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAA29BE8-57E0-4D62-AD3F-03D443FC25D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5599A49-8769-41FA-9A77-460C77A4C51B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57330" yWindow="-270" windowWidth="21030" windowHeight="11340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -417,7 +417,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -427,6 +427,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -445,7 +451,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -465,6 +471,15 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -1056,233 +1071,233 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A14" t="s">
+    <row r="14" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.75">
+      <c r="A14" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="D14" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="D14" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="G14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A15" t="s">
+      <c r="G14" s="11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.75">
+      <c r="A15" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="D15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="D15" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="G15" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="29.5" x14ac:dyDescent="0.75">
-      <c r="A16" t="s">
+      <c r="G15" s="11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" s="11" customFormat="1" ht="29.5" x14ac:dyDescent="0.75">
+      <c r="A16" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="D16" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="D16" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="F16" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="G16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A17" t="s">
+      <c r="G16" s="11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.75">
+      <c r="A17" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="D17" t="s">
-        <v>14</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="D17" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F17" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="G17" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A18" t="s">
+      <c r="G17" s="11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.75">
+      <c r="A18" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="D18" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="D18" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="F18" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="G18" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A19" t="s">
+      <c r="G18" s="11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.75">
+      <c r="A19" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="D19" t="s">
-        <v>14</v>
-      </c>
-      <c r="E19" t="s">
+      <c r="D19" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="F19" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="G19" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="29.5" x14ac:dyDescent="0.75">
-      <c r="A20" t="s">
+      <c r="G19" s="11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" s="11" customFormat="1" ht="29.5" x14ac:dyDescent="0.75">
+      <c r="A20" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="D20" t="s">
-        <v>14</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="D20" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="F20" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="G20" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.75">
-      <c r="A21" t="s">
+      <c r="G20" s="11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.75">
+      <c r="A21" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="D21" t="s">
-        <v>14</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="D21" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="F21" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="G21" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A22" t="s">
+      <c r="G21" s="11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" s="11" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A22" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="D22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="D22" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="F22" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="G22" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="29.5" x14ac:dyDescent="0.75">
-      <c r="A23" t="s">
+      <c r="G22" s="11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" s="11" customFormat="1" ht="29.5" x14ac:dyDescent="0.75">
+      <c r="A23" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="D23" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="D23" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="F23" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" s="11" t="s">
         <v>14</v>
       </c>
     </row>
